--- a/plantillas/57.xlsx
+++ b/plantillas/57.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Cargue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Listas" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Productos" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="MARCA_1">Listas!$D$2:$D$3</definedName>
@@ -22,12 +22,12 @@
     <definedName name="MARCA_8">Listas!$K$2:$K$4</definedName>
     <definedName name="MARCA_9">Listas!$L$2:$L$6</definedName>
     <definedName name="MARCA_10">Listas!$M$2:$M$2</definedName>
-    <definedName name="MARCA_11">Listas!$N$2:$N$19</definedName>
+    <definedName name="MARCA_11">Listas!$N$2:$N$18</definedName>
     <definedName name="MARCA_12">Listas!$O$2:$O$14</definedName>
     <definedName name="MARCA_13">Listas!$P$2:$P$2</definedName>
     <definedName name="MARCA_14">Listas!$Q$2:$Q$3</definedName>
     <definedName name="MARCA_15">Listas!$R$2:$R$2</definedName>
-    <definedName name="MARCA_16">Listas!$S$2:$S$8</definedName>
+    <definedName name="MARCA_16">Listas!$S$2:$S$7</definedName>
     <definedName name="MARCA_17">Listas!$T$2:$T$9</definedName>
     <definedName name="MARCA_18">Listas!$U$2:$U$2</definedName>
     <definedName name="MARCA_19">Listas!$V$2:$V$6</definedName>
@@ -638,11 +638,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B3,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B3,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B3,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B3,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -662,11 +662,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B4,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B4,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B4,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B4,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -686,11 +686,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B5,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B5,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B5,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B5,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -710,11 +710,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B6,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B6,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B6,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B6,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -729,11 +729,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B7,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B7,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B7,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B7,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -748,11 +748,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B8,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B8,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B8,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B8,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -767,11 +767,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B9,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B9,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B9,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B9,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -786,11 +786,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B10,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B10,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B10,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B10,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -805,11 +805,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B11,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B11,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B11,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B11,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -824,11 +824,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B12,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B12,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B12,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B12,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -843,11 +843,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B13,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B13,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B13,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B13,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -862,11 +862,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B14,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B14,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B14,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B14,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -881,11 +881,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B15,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B15,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B15,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B15,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -900,11 +900,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B16,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B16,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B16,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B16,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -919,11 +919,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B17,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B17,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B17,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B17,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -938,11 +938,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B18,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B18,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B18,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B18,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -957,11 +957,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B19,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B19,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B19,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B19,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -976,11 +976,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B20,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B20,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B20,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B20,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -995,11 +995,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B21,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B21,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B21,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B21,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1014,11 +1014,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B22,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B22,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B22,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B22,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1033,11 +1033,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B23,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B23,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B23,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B23,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1052,11 +1052,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B24,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B24,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B24,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B24,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1071,11 +1071,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B25,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B25,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B25,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B25,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1090,11 +1090,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B26,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B26,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B26,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B26,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1109,11 +1109,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B27,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B27,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B27,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B27,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1128,11 +1128,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B28,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B28,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B28,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B28,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1147,11 +1147,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B29,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B29,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B29,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B29,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1166,11 +1166,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B30,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B30,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B30,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B30,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1185,11 +1185,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B31,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B31,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B31,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B31,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1204,11 +1204,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B32,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B32,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B32,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B32,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1223,11 +1223,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B33,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B33,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B33,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B33,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1242,11 +1242,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B34,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B34,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B34,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B34,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1261,11 +1261,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B35,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B35,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B35,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B35,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1280,11 +1280,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B36,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B36,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B36,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B36,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1299,11 +1299,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B37,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B37,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B37,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B37,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1318,11 +1318,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B38,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B38,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B38,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B38,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1337,11 +1337,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B39,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B39,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B39,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B39,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1356,11 +1356,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B40,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B40,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B40,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B40,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1375,11 +1375,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B41,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B41,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B41,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B41,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1394,11 +1394,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B42,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B42,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B42,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B42,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1413,11 +1413,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B43,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B43,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B43,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B43,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1432,11 +1432,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B44,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B44,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B44,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B44,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1451,11 +1451,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B45,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B45,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B45,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B45,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1470,11 +1470,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B46,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B46,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B46,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B46,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1489,11 +1489,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B47,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B47,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B47,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B47,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1508,11 +1508,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B48,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B48,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B48,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B48,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1527,11 +1527,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B49,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B49,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B49,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B49,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1546,11 +1546,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B50,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B50,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B50,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B50,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1565,11 +1565,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B51,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B51,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B51,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B51,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1584,11 +1584,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B52,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B52,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B52,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B52,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1603,11 +1603,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B53,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B53,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B53,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B53,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1622,11 +1622,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B54,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B54,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B54,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B54,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1641,11 +1641,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B55,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B55,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B55,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B55,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1660,11 +1660,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B56,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B56,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B56,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B56,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1679,11 +1679,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B57,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B57,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B57,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B57,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1698,11 +1698,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B58,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B58,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B58,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B58,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1717,11 +1717,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B59,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B59,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B59,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B59,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1736,11 +1736,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B60,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B60,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B60,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B60,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1755,11 +1755,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B61,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B61,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B61,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B61,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1774,11 +1774,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B62,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B62,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B62,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B62,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1793,11 +1793,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B63,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B63,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B63,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B63,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1812,11 +1812,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B64,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B64,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B64,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B64,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1831,11 +1831,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B65,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B65,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B65,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B65,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1850,11 +1850,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B66,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B66,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B66,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B66,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1869,11 +1869,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B67,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B67,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B67,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B67,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1888,11 +1888,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B68,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B68,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B68,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B68,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1907,11 +1907,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B69,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B69,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B69,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B69,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1926,11 +1926,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B70,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B70,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B70,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B70,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1945,11 +1945,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B71,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B71,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B71,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B71,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1964,11 +1964,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B72,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B72,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B72,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B72,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1983,11 +1983,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B73,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B73,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B73,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B73,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2002,11 +2002,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B74,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B74,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B74,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B74,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2021,11 +2021,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B75,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B75,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B75,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B75,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2040,11 +2040,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B76,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B76,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B76,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B76,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2059,11 +2059,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B77,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B77,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B77,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B77,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2078,11 +2078,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B78,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B78,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B78,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B78,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2097,11 +2097,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B79,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B79,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B79,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B79,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2116,11 +2116,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B80,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B80,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B80,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B80,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2135,11 +2135,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B81,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B81,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B81,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B81,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2154,11 +2154,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B82,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B82,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B82,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B82,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2173,11 +2173,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B83,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B83,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B83,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B83,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2192,11 +2192,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B84,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B84,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B84,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B84,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2211,11 +2211,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B85,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B85,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B85,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B85,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2230,11 +2230,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B86,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B86,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B86,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B86,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2249,11 +2249,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B87,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B87,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B87,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B87,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2268,11 +2268,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B88,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B88,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B88,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B88,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2287,11 +2287,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B89,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B89,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B89,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B89,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2306,11 +2306,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B90,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B90,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B90,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B90,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2325,11 +2325,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B91,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B91,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B91,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B91,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2344,11 +2344,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B92,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B92,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B92,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B92,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2363,11 +2363,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B93,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B93,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B93,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B93,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2382,11 +2382,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B94,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B94,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B94,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B94,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2401,11 +2401,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B95,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B95,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B95,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B95,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2420,11 +2420,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B96,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B96,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B96,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B96,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2439,11 +2439,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B97,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B97,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B97,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B97,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2458,11 +2458,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B98,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B98,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B98,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B98,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2477,11 +2477,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B99,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B99,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B99,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B99,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2496,11 +2496,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B100,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B100,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B100,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B100,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2515,11 +2515,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B101,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B101,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B101,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B101,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2534,11 +2534,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B102,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B102,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B102,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B102,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2553,11 +2553,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B103,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B103,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B103,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B103,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2572,11 +2572,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B104,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B104,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B104,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B104,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2591,11 +2591,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B105,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B105,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B105,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B105,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2610,11 +2610,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B106,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B106,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B106,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B106,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2629,11 +2629,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B107,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B107,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B107,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B107,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2648,11 +2648,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B108,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B108,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B108,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B108,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2667,11 +2667,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B109,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B109,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B109,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B109,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2686,11 +2686,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B110,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B110,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B110,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B110,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2705,11 +2705,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B111,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B111,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B111,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B111,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2724,11 +2724,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B112,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B112,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B112,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B112,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2743,11 +2743,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B113,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B113,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B113,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B113,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2762,11 +2762,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B114,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B114,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B114,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B114,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2781,11 +2781,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B115,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B115,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B115,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B115,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2800,11 +2800,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B116,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B116,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B116,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B116,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2819,11 +2819,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B117,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B117,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B117,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B117,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2838,11 +2838,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B118,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B118,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B118,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B118,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2857,11 +2857,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B119,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B119,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B119,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B119,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2876,11 +2876,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B120,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B120,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B120,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B120,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2895,11 +2895,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B121,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B121,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B121,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B121,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2914,11 +2914,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B122,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B122,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B122,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B122,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2933,11 +2933,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B123,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B123,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B123,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B123,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2952,11 +2952,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B124,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B124,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B124,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B124,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -2971,11 +2971,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B125,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B125,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B125,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B125,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -2990,11 +2990,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B126,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B126,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B126,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B126,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3009,11 +3009,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B127,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B127,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B127,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B127,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3028,11 +3028,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B128,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B128,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B128,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B128,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3047,11 +3047,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B129,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B129,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B129,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B129,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3066,11 +3066,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B130,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B130,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B130,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B130,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3085,11 +3085,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B131,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B131,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B131,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B131,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3104,11 +3104,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B132,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B132,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B132,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B132,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3123,11 +3123,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B133,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B133,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B133,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B133,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3142,11 +3142,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B134,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B134,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B134,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B134,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3161,11 +3161,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B135,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B135,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B135,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B135,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3180,11 +3180,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B136,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B136,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B136,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B136,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3199,11 +3199,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B137,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B137,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B137,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B137,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3218,11 +3218,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B138,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B138,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B138,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B138,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3237,11 +3237,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B139,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B139,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B139,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B139,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3256,11 +3256,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B140,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B140,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B140,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B140,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3275,11 +3275,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B141,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B141,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B141,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B141,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3294,11 +3294,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B142,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B142,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B142,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B142,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3313,11 +3313,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B143,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B143,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B143,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B143,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3332,11 +3332,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B144,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B144,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B144,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B144,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3351,11 +3351,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B145,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B145,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B145,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B145,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3370,11 +3370,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B146,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B146,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B146,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B146,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3389,11 +3389,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B147,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B147,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B147,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B147,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3408,11 +3408,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B148,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B148,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B148,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B148,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3427,11 +3427,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B149,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B149,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B149,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B149,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3446,11 +3446,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B150,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B150,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B150,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B150,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3465,11 +3465,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B151,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B151,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B151,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B151,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3484,11 +3484,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B152,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B152,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B152,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B152,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3503,11 +3503,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B153,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B153,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B153,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B153,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3522,11 +3522,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B154,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B154,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B154,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B154,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3541,11 +3541,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B155,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B155,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B155,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B155,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3560,11 +3560,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B156,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B156,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B156,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B156,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3579,11 +3579,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B157,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B157,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B157,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B157,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3598,11 +3598,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B158,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B158,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B158,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B158,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3617,11 +3617,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B159,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B159,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B159,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B159,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3636,11 +3636,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B160,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B160,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B160,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B160,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3655,11 +3655,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B161,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B161,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B161,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B161,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3674,11 +3674,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B162,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B162,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B162,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B162,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3693,11 +3693,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B163,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B163,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B163,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B163,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3712,11 +3712,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B164,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B164,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B164,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B164,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3731,11 +3731,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B165,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B165,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B165,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B165,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3750,11 +3750,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B166,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B166,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B166,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B166,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3769,11 +3769,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B167,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B167,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B167,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B167,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3788,11 +3788,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B168,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B168,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B168,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B168,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3807,11 +3807,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B169,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B169,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B169,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B169,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3826,11 +3826,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B170,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B170,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B170,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B170,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3845,11 +3845,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B171,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B171,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B171,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B171,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3864,11 +3864,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B172,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B172,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B172,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B172,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3883,11 +3883,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B173,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B173,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B173,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B173,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3902,11 +3902,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B174,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B174,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B174,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B174,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3921,11 +3921,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B175,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B175,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B175,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B175,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3940,11 +3940,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B176,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B176,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B176,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B176,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3959,11 +3959,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B177,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B177,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B177,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B177,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -3978,11 +3978,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B178,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B178,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B178,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B178,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -3997,11 +3997,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B179,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B179,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B179,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B179,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4016,11 +4016,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B180,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B180,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B180,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B180,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4035,11 +4035,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B181,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B181,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B181,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B181,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4054,11 +4054,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B182,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B182,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B182,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B182,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4073,11 +4073,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B183,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B183,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B183,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B183,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4092,11 +4092,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B184,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B184,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B184,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B184,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4111,11 +4111,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B185,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B185,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B185,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B185,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4130,11 +4130,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B186,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B186,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B186,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B186,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4149,11 +4149,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B187,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B187,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B187,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B187,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4168,11 +4168,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B188,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B188,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B188,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B188,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4187,11 +4187,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B189,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B189,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B189,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B189,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4206,11 +4206,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B190,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B190,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B190,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B190,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4225,11 +4225,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B191,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B191,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B191,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B191,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4244,11 +4244,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B192,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B192,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B192,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B192,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4263,11 +4263,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B193,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B193,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B193,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B193,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4282,11 +4282,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B194,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B194,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B194,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B194,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4301,11 +4301,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B195,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B195,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B195,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B195,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4320,11 +4320,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B196,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B196,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B196,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B196,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4339,11 +4339,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B197,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B197,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B197,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B197,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4358,11 +4358,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B198,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B198,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B198,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B198,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4377,11 +4377,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B199,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B199,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B199,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B199,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4396,11 +4396,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B200,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B200,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B200,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B200,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4415,11 +4415,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B201,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B201,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B201,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B201,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4434,11 +4434,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B202,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B202,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B202,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B202,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4453,11 +4453,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B203,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B203,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B203,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B203,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4472,11 +4472,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B204,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B204,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B204,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B204,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4491,11 +4491,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B205,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B205,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B205,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B205,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4510,11 +4510,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B206,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B206,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B206,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B206,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4529,11 +4529,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B207,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B207,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B207,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B207,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4548,11 +4548,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B208,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B208,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B208,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B208,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4567,11 +4567,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B209,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B209,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B209,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B209,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4586,11 +4586,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B210,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B210,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B210,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B210,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4605,11 +4605,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B211,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B211,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B211,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B211,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4624,11 +4624,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B212,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B212,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B212,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B212,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4643,11 +4643,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B213,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B213,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B213,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B213,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4662,11 +4662,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B214,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B214,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B214,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B214,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4681,11 +4681,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B215,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B215,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B215,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B215,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4700,11 +4700,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B216,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B216,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B216,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B216,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4719,11 +4719,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B217,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B217,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B217,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B217,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4738,11 +4738,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B218,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B218,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B218,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B218,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4757,11 +4757,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B219,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B219,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B219,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B219,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4776,11 +4776,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B220,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B220,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B220,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B220,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4795,11 +4795,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B221,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B221,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B221,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B221,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4814,11 +4814,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B222,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B222,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B222,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B222,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4833,11 +4833,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B223,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B223,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B223,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B223,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4852,11 +4852,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B224,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B224,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B224,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B224,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4871,11 +4871,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B225,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B225,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B225,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B225,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4890,11 +4890,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B226,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B226,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B226,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B226,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4909,11 +4909,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B227,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B227,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B227,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B227,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4928,11 +4928,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B228,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B228,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B228,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B228,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4947,11 +4947,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B229,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B229,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B229,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B229,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -4966,11 +4966,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B230,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B230,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B230,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B230,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -4985,11 +4985,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B231,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B231,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B231,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B231,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5004,11 +5004,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B232,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B232,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B232,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B232,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5023,11 +5023,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B233,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B233,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B233,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B233,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5042,11 +5042,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B234,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B234,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B234,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B234,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5061,11 +5061,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B235,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B235,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B235,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B235,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5080,11 +5080,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B236,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B236,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B236,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B236,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5099,11 +5099,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B237,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B237,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B237,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B237,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5118,11 +5118,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B238,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B238,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B238,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B238,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5137,11 +5137,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B239,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B239,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B239,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B239,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5156,11 +5156,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B240,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B240,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B240,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B240,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5175,11 +5175,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B241,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B241,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B241,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B241,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5194,11 +5194,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B242,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B242,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B242,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B242,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5213,11 +5213,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B243,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B243,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B243,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B243,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5232,11 +5232,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B244,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B244,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B244,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B244,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5251,11 +5251,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B245,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B245,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B245,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B245,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5270,11 +5270,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B246,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B246,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B246,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B246,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5289,11 +5289,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B247,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B247,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B247,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B247,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5308,11 +5308,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B248,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B248,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B248,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B248,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5327,11 +5327,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B249,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B249,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B249,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B249,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5346,11 +5346,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B250,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B250,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B250,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B250,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5365,11 +5365,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B251,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B251,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B251,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B251,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5384,11 +5384,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B252,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B252,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B252,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B252,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5403,11 +5403,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B253,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B253,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B253,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B253,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5422,11 +5422,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B254,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B254,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B254,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B254,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5441,11 +5441,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B255,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B255,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B255,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B255,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5460,11 +5460,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B256,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B256,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B256,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B256,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5479,11 +5479,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B257,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B257,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B257,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B257,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5498,11 +5498,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B258,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B258,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B258,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B258,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5517,11 +5517,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B259,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B259,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B259,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B259,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5536,11 +5536,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B260,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B260,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B260,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B260,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5555,11 +5555,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B261,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B261,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B261,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B261,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5574,11 +5574,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B262,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B262,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B262,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B262,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5593,11 +5593,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B263,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B263,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B263,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B263,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5612,11 +5612,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B264,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B264,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B264,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B264,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5631,11 +5631,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B265,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B265,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B265,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B265,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5650,11 +5650,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B266,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B266,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B266,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B266,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5669,11 +5669,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B267,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B267,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B267,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B267,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5688,11 +5688,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B268,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B268,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B268,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B268,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5707,11 +5707,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B269,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B269,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B269,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B269,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5726,11 +5726,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B270,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B270,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B270,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B270,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5745,11 +5745,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B271,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B271,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B271,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B271,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5764,11 +5764,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B272,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B272,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B272,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B272,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5783,11 +5783,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B273,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B273,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B273,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B273,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5802,11 +5802,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B274,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B274,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B274,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B274,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5821,11 +5821,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B275,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B275,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B275,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B275,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5840,11 +5840,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B276,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B276,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B276,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B276,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5859,11 +5859,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B277,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B277,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B277,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B277,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5878,11 +5878,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B278,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B278,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B278,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B278,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5897,11 +5897,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B279,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B279,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B279,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B279,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5916,11 +5916,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B280,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B280,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B280,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B280,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5935,11 +5935,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B281,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B281,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B281,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B281,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5954,11 +5954,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B282,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B282,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B282,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B282,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -5973,11 +5973,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B283,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B283,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B283,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B283,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -5992,11 +5992,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B284,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B284,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B284,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B284,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6011,11 +6011,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B285,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B285,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B285,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B285,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6030,11 +6030,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B286,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B286,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B286,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B286,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6049,11 +6049,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B287,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B287,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B287,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B287,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6068,11 +6068,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B288,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B288,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B288,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B288,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6087,11 +6087,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B289,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B289,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B289,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B289,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6106,11 +6106,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B290,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B290,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B290,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B290,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6125,11 +6125,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B291,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B291,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B291,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B291,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6144,11 +6144,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B292,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B292,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B292,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B292,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6163,11 +6163,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B293,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B293,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B293,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B293,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6182,11 +6182,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B294,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B294,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B294,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B294,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6201,11 +6201,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B295,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B295,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B295,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B295,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6220,11 +6220,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B296,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B296,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B296,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B296,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6239,11 +6239,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B297,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B297,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B297,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B297,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6258,11 +6258,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B298,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B298,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B298,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B298,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6277,11 +6277,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B299,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B299,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B299,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B299,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6296,11 +6296,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B300,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B300,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B300,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B300,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6315,11 +6315,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B301,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B301,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B301,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B301,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6334,11 +6334,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B302,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B302,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B302,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B302,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6353,11 +6353,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B303,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B303,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B303,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B303,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6372,11 +6372,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B304,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B304,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B304,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B304,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6391,11 +6391,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B305,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B305,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B305,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B305,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6410,11 +6410,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B306,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B306,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B306,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B306,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6429,11 +6429,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B307,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B307,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B307,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B307,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6448,11 +6448,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B308,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B308,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B308,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B308,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6467,11 +6467,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B309,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B309,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B309,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B309,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6486,11 +6486,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B310,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B310,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B310,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B310,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6505,11 +6505,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B311,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B311,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B311,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B311,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6524,11 +6524,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B312,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B312,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B312,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B312,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6543,11 +6543,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B313,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B313,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B313,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B313,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6562,11 +6562,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B314,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B314,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B314,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B314,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6581,11 +6581,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B315,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B315,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B315,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B315,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6600,11 +6600,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B316,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B316,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B316,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B316,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6619,11 +6619,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B317,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B317,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B317,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B317,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6638,11 +6638,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B318,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B318,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B318,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B318,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6657,11 +6657,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B319,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B319,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B319,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B319,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6676,11 +6676,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B320,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B320,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B320,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B320,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6695,11 +6695,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B321,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B321,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B321,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B321,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6714,11 +6714,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B322,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B322,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B322,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B322,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6733,11 +6733,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B323,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B323,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B323,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B323,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6752,11 +6752,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B324,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B324,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B324,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B324,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6771,11 +6771,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B325,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B325,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B325,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B325,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6790,11 +6790,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B326,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B326,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B326,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B326,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6809,11 +6809,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B327,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B327,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B327,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B327,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6828,11 +6828,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B328,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B328,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B328,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B328,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6847,11 +6847,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B329,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B329,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B329,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B329,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6866,11 +6866,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B330,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B330,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B330,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B330,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6885,11 +6885,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B331,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B331,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B331,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B331,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6904,11 +6904,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B332,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B332,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B332,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B332,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6923,11 +6923,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B333,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B333,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B333,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B333,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6942,11 +6942,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B334,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B334,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B334,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B334,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6961,11 +6961,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B335,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B335,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B335,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B335,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -6980,11 +6980,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B336,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B336,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B336,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B336,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -6999,11 +6999,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B337,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B337,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B337,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B337,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7018,11 +7018,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B338,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B338,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B338,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B338,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7037,11 +7037,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B339,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B339,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B339,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B339,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7056,11 +7056,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B340,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B340,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B340,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B340,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7075,11 +7075,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B341,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B341,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B341,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B341,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7094,11 +7094,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B342,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B342,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B342,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B342,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7113,11 +7113,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B343,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B343,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B343,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B343,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7132,11 +7132,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B344,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B344,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B344,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B344,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7151,11 +7151,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B345,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B345,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B345,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B345,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7170,11 +7170,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B346,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B346,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B346,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B346,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7189,11 +7189,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B347,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B347,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B347,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B347,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7208,11 +7208,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B348,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B348,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B348,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B348,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7227,11 +7227,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B349,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B349,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B349,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B349,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7246,11 +7246,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B350,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B350,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B350,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B350,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7265,11 +7265,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B351,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B351,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B351,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B351,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7284,11 +7284,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B352,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B352,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B352,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B352,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7303,11 +7303,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B353,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B353,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B353,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B353,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7322,11 +7322,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B354,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B354,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B354,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B354,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7341,11 +7341,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B355,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B355,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B355,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B355,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7360,11 +7360,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B356,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B356,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B356,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B356,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7379,11 +7379,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B357,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B357,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B357,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B357,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7398,11 +7398,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B358,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B358,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B358,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B358,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7417,11 +7417,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B359,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B359,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B359,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B359,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7436,11 +7436,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B360,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B360,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B360,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B360,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7455,11 +7455,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B361,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B361,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B361,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B361,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7474,11 +7474,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B362,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B362,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B362,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B362,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7493,11 +7493,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B363,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B363,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B363,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B363,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7512,11 +7512,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B364,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B364,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B364,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B364,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7531,11 +7531,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B365,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B365,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B365,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B365,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7550,11 +7550,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B366,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B366,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B366,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B366,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7569,11 +7569,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B367,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B367,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B367,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B367,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7588,11 +7588,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B368,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B368,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B368,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B368,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7607,11 +7607,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B369,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B369,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B369,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B369,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7626,11 +7626,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B370,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B370,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B370,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B370,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7645,11 +7645,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B371,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B371,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B371,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B371,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7664,11 +7664,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B372,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B372,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B372,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B372,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7683,11 +7683,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B373,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B373,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B373,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B373,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7702,11 +7702,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B374,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B374,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B374,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B374,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7721,11 +7721,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B375,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B375,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B375,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B375,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7740,11 +7740,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B376,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B376,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B376,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B376,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7759,11 +7759,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B377,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B377,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B377,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B377,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7778,11 +7778,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B378,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B378,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B378,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B378,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7797,11 +7797,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B379,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B379,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B379,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B379,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7816,11 +7816,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B380,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B380,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B380,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B380,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7835,11 +7835,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B381,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B381,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B381,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B381,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7854,11 +7854,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B382,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B382,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B382,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B382,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7873,11 +7873,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B383,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B383,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B383,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B383,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7892,11 +7892,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B384,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B384,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B384,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B384,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7911,11 +7911,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B385,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B385,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B385,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B385,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7930,11 +7930,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B386,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B386,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B386,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B386,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7949,11 +7949,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B387,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B387,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B387,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B387,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -7968,11 +7968,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B388,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B388,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B388,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B388,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -7987,11 +7987,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B389,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B389,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B389,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B389,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8006,11 +8006,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B390,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B390,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B390,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B390,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8025,11 +8025,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B391,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B391,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B391,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B391,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8044,11 +8044,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B392,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B392,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B392,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B392,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8063,11 +8063,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B393,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B393,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B393,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B393,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8082,11 +8082,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B394,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B394,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B394,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B394,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8101,11 +8101,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B395,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B395,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B395,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B395,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8120,11 +8120,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B396,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B396,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B396,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B396,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8139,11 +8139,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B397,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B397,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B397,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B397,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8158,11 +8158,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B398,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B398,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B398,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B398,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8177,11 +8177,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B399,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B399,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B399,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B399,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8196,11 +8196,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B400,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B400,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B400,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B400,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8215,11 +8215,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B401,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B401,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B401,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B401,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8234,11 +8234,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$92,MATCH(B402,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B402,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$92,MATCH(B402,Productos!$A$2:$A$92,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B402,Productos!$A$2:$A$90,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>ROCKY ALIM P/CACHORROS 1.5KG · 93512600000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>ROCKY ALIM P/CACHORROS 1.5KG · 93512600000</t>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -8853,11 +8853,6 @@
           <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
@@ -9031,7 +9026,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
         </is>
       </c>
     </row>
@@ -9048,7 +9043,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9060,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
     </row>
@@ -9078,11 +9073,6 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>MARCA_18</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D96"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9418,7 +9408,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -9578,7 +9568,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -9838,7 +9828,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9958,7 +9948,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9978,7 +9968,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10069,16 +10059,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 2KG · 90415960000</t>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90415960000</t>
+          <t>90410810000</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -10089,16 +10079,16 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>90410810000</t>
+          <t>93510840000</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -10109,16 +10099,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>93510840000</t>
+          <t>93510830000</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -10129,36 +10119,36 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>93510830000</t>
+          <t>90034090000</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
+          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>90034090000</t>
+          <t>90033960000</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -10169,16 +10159,16 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
+          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>90033960000</t>
+          <t>90034200000</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10189,16 +10179,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
+          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>90034200000</t>
+          <t>90034180000</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -10209,16 +10199,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
+          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>90034180000</t>
+          <t>90034290000</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10229,16 +10219,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
+          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>90034290000</t>
+          <t>90034190000</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10249,16 +10239,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
+          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>90034190000</t>
+          <t>90034130000</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -10269,16 +10259,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 40LB · 90034150000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>90034130000</t>
+          <t>90034150000</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10289,16 +10279,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 40LB · 90034150000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>90034150000</t>
+          <t>90034160000</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -10309,12 +10299,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
+          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>90034160000</t>
+          <t>90033990000</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -10329,16 +10319,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
+          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>90033990000</t>
+          <t>90034210000</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -10349,12 +10339,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
+          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>90034210000</t>
+          <t>90034250000</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -10369,16 +10359,16 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
+          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>90034250000</t>
+          <t>90034230000</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -10389,52 +10379,52 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
+          <t>OLA LOROS GUACAMAYA/PARROTS 800GRS · 90405590000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>90034230000</t>
+          <t>90405590000</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>OLA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>OLA LOROS GUACAMAYA/PARROTS 800GRS · 90405590000</t>
+          <t>NECTAR INSTANTANEO DE COLIBRI 2LB · 90710077000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>90405590000</t>
+          <t>90710077000</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PERKY PET</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NECTAR INSTANTANEO DE COLIBRI 2LB · 90710077000</t>
+          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>90710077000</t>
+          <t>93502370000</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -10449,56 +10439,56 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>93502370000</t>
+          <t>93512180000</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>RED BARN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>93512180000</t>
+          <t>93511630000</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
+          <t>D SK ALIM LATA RES/HIGADO POLLO 400GR · 93511640000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>93511630000</t>
+          <t>93511640000</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -10509,16 +10499,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES/HIGADO POLLO 400GR · 93511640000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>93511640000</t>
+          <t>93500000342</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10529,16 +10519,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ROCKY ADULTO POLLO US 2KG · 90022370000</t>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>90022370000</t>
+          <t>93500000341</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10549,16 +10539,16 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>ROCKY ALIM P/CACHORROS 1.5KG · 93512600000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>93500000342</t>
+          <t>93512600000</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10569,16 +10559,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>93500000341</t>
+          <t>93511670000</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10589,56 +10579,56 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ROCKY ALIM P/CACHORROS 1.5KG · 93512600000</t>
+          <t>D SUPRA ADULTO 10KG · 93508880000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>93512600000</t>
+          <t>93508880000</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>93511670000</t>
+          <t>93509320000</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>D SUPRA ADULTO 10KG · 93508880000</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>93508880000</t>
+          <t>93508860000</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10649,16 +10639,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>93509320000</t>
+          <t>93508890000</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10669,16 +10659,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
+          <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>93508860000</t>
+          <t>93508900000</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10689,16 +10679,16 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
+          <t>SUPRA ADULTO 4KG · 93508870000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>93508890000</t>
+          <t>93508870000</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10709,16 +10699,16 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
+          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>93508900000</t>
+          <t>93508910000</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10729,12 +10719,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
+          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>93508870000</t>
+          <t>93508920000</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -10749,76 +10739,76 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
+          <t>SHED-X SUPLEMENTO PERROS GRANDES · 90334000000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>93508910000</t>
+          <t>90334000000</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SYNERGY</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
+          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>93508920000</t>
+          <t>90409640000</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SHED-X SUPLEMENTO PERROS GRANDES · 90334000000</t>
+          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>90334000000</t>
+          <t>90409900000</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SYNERGY</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>90409640000</t>
+          <t>90410990000</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10829,16 +10819,16 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
+          <t>TETRAFIN PELLET FLOTANTE 1.87OZ · 90410020000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>90409900000</t>
+          <t>90410020000</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10849,16 +10839,16 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
+          <t>TETRAMIN HOJUELAS 3.53 OZ. · 90720600000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>90410990000</t>
+          <t>90720600000</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10869,78 +10859,58 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TETRAFIN PELLET FLOTANTE 1.87OZ · 90410020000</t>
+          <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>90410020000</t>
+          <t>90409060000</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>WHISKAS</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TETRAMIN HOJUELAS 3.53 OZ. · 90720600000</t>
+          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>90720600000</t>
+          <t>90409050000</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>WHISKAS</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
+          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>90409060000</t>
+          <t>90409070000</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D90" t="inlineStr">
-        <is>
-          <t>WHISKAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>90409050000</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>21</v>
-      </c>
-      <c r="D91" t="inlineStr">
         <is>
           <t>WHISKAS</t>
         </is>
@@ -10949,54 +10919,34 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
+          <t>Sucursal</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>90409070000</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>22</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>WHISKAS</t>
-        </is>
+          <t>MELO &amp; CIA. | PASO CANOAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sucursal</t>
+          <t>Inventario al</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MELO &amp; CIA. | PASO CANOAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Inventario al</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>24.10.2026</t>
+          <t>28.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/57.xlsx
+++ b/plantillas/57.xlsx
@@ -9488,7 +9488,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>28.10.2026</t>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>

--- a/plantillas/57.xlsx
+++ b/plantillas/57.xlsx
@@ -15,25 +15,24 @@
     <definedName name="MARCA_1">Listas!$D$2:$D$3</definedName>
     <definedName name="MARCA_2">Listas!$E$2:$E$5</definedName>
     <definedName name="MARCA_3">Listas!$F$2:$F$5</definedName>
-    <definedName name="MARCA_4">Listas!$G$2:$G$7</definedName>
+    <definedName name="MARCA_4">Listas!$G$2:$G$6</definedName>
     <definedName name="MARCA_5">Listas!$H$2:$H$2</definedName>
     <definedName name="MARCA_6">Listas!$I$2:$I$6</definedName>
     <definedName name="MARCA_7">Listas!$J$2:$J$2</definedName>
     <definedName name="MARCA_8">Listas!$K$2:$K$4</definedName>
     <definedName name="MARCA_9">Listas!$L$2:$L$6</definedName>
-    <definedName name="MARCA_10">Listas!$M$2:$M$2</definedName>
-    <definedName name="MARCA_11">Listas!$N$2:$N$18</definedName>
-    <definedName name="MARCA_12">Listas!$O$2:$O$14</definedName>
-    <definedName name="MARCA_13">Listas!$P$2:$P$2</definedName>
-    <definedName name="MARCA_14">Listas!$Q$2:$Q$3</definedName>
-    <definedName name="MARCA_15">Listas!$R$2:$R$2</definedName>
-    <definedName name="MARCA_16">Listas!$S$2:$S$7</definedName>
-    <definedName name="MARCA_17">Listas!$T$2:$T$9</definedName>
-    <definedName name="MARCA_18">Listas!$U$2:$U$2</definedName>
-    <definedName name="MARCA_19">Listas!$V$2:$V$6</definedName>
-    <definedName name="MARCA_20">Listas!$W$2:$W$4</definedName>
+    <definedName name="MARCA_10">Listas!$M$2:$M$18</definedName>
+    <definedName name="MARCA_11">Listas!$N$2:$N$14</definedName>
+    <definedName name="MARCA_12">Listas!$O$2:$O$2</definedName>
+    <definedName name="MARCA_13">Listas!$P$2:$P$3</definedName>
+    <definedName name="MARCA_14">Listas!$Q$2:$Q$2</definedName>
+    <definedName name="MARCA_15">Listas!$R$2:$R$7</definedName>
+    <definedName name="MARCA_16">Listas!$S$2:$S$9</definedName>
+    <definedName name="MARCA_17">Listas!$T$2:$T$2</definedName>
+    <definedName name="MARCA_18">Listas!$U$2:$U$6</definedName>
+    <definedName name="MARCA_19">Listas!$V$2:$V$4</definedName>
     <definedName name="MESES">Listas!$C$2:$C$5</definedName>
-    <definedName name="MARCAS">Listas!$A$2:$A$21</definedName>
+    <definedName name="MARCAS">Listas!$A$2:$A$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -638,11 +637,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B3,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B3,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B3,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B3,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -662,11 +661,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B4,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B4,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B4,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B4,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -686,11 +685,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B5,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B5,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B5,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B5,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -710,11 +709,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B6,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B6,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B6,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B6,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -729,11 +728,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B7,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B7,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B7,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B7,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -748,11 +747,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B8,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B8,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B8,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B8,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -767,11 +766,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B9,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B9,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B9,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B9,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -786,11 +785,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B10,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B10,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B10,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B10,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -805,11 +804,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B11,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B11,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B11,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B11,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -824,11 +823,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B12,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B12,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B12,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B12,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -843,11 +842,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B13,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B13,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B13,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B13,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -862,11 +861,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B14,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B14,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B14,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B14,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -881,11 +880,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B15,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B15,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B15,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B15,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -900,11 +899,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B16,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B16,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B16,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B16,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -919,11 +918,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B17,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B17,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B17,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B17,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -938,11 +937,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B18,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B18,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B18,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B18,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -957,11 +956,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B19,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B19,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B19,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B19,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -976,11 +975,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B20,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B20,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B20,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B20,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -995,11 +994,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B21,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B21,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B21,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B21,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1014,11 +1013,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B22,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B22,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B22,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B22,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1033,11 +1032,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B23,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B23,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B23,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B23,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1052,11 +1051,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B24,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B24,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B24,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B24,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1071,11 +1070,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B25,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B25,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B25,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B25,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1090,11 +1089,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B26,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B26,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B26,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B26,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1109,11 +1108,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B27,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B27,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B27,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B27,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1128,11 +1127,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B28,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B28,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B28,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B28,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1147,11 +1146,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B29,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B29,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B29,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B29,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1166,11 +1165,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B30,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B30,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B30,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B30,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1185,11 +1184,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B31,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B31,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B31,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B31,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1204,11 +1203,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B32,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B32,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B32,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B32,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1223,11 +1222,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B33,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B33,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B33,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B33,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1242,11 +1241,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B34,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B34,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B34,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B34,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1261,11 +1260,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B35,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B35,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B35,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B35,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1280,11 +1279,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B36,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B36,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B36,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B36,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1299,11 +1298,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B37,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B37,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B37,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B37,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1318,11 +1317,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B38,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B38,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B38,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B38,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1337,11 +1336,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B39,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B39,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B39,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B39,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1356,11 +1355,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B40,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B40,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B40,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B40,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1375,11 +1374,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B41,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B41,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B41,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B41,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1394,11 +1393,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B42,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B42,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B42,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B42,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1413,11 +1412,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B43,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B43,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B43,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B43,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1432,11 +1431,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B44,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B44,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B44,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B44,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1451,11 +1450,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B45,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B45,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B45,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B45,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1470,11 +1469,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B46,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B46,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B46,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B46,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1489,11 +1488,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B47,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B47,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B47,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B47,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1508,11 +1507,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B48,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B48,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B48,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B48,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1527,11 +1526,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B49,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B49,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B49,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B49,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1546,11 +1545,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B50,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B50,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B50,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B50,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1565,11 +1564,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B51,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B51,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B51,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B51,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1584,11 +1583,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B52,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B52,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B52,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B52,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1603,11 +1602,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B53,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B53,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B53,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B53,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1622,11 +1621,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B54,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B54,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B54,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B54,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1641,11 +1640,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B55,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B55,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B55,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B55,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1660,11 +1659,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B56,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B56,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B56,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B56,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1679,11 +1678,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B57,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B57,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B57,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B57,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1698,11 +1697,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B58,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B58,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B58,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B58,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1717,11 +1716,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B59,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B59,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B59,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B59,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1736,11 +1735,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B60,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B60,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B60,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B60,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1755,11 +1754,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B61,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B61,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B61,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B61,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1774,11 +1773,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B62,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B62,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B62,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B62,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1793,11 +1792,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B63,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B63,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B63,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B63,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1812,11 +1811,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B64,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B64,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B64,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B64,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1831,11 +1830,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B65,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B65,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B65,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B65,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1850,11 +1849,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B66,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B66,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B66,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B66,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1869,11 +1868,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B67,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B67,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B67,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B67,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1888,11 +1887,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B68,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B68,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B68,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B68,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1907,11 +1906,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B69,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B69,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B69,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B69,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1926,11 +1925,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B70,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B70,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B70,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B70,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1945,11 +1944,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B71,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B71,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B71,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B71,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1964,11 +1963,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B72,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B72,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B72,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B72,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -1983,11 +1982,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B73,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B73,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B73,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B73,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2002,11 +2001,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B74,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B74,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B74,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B74,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2021,11 +2020,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B75,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B75,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B75,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B75,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2040,11 +2039,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B76,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B76,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B76,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B76,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2059,11 +2058,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B77,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B77,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B77,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B77,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2078,11 +2077,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B78,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B78,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B78,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B78,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2097,11 +2096,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B79,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B79,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B79,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B79,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2116,11 +2115,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B80,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B80,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B80,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B80,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2135,11 +2134,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B81,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B81,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B81,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B81,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2154,11 +2153,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B82,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B82,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B82,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B82,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2173,11 +2172,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B83,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B83,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B83,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B83,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2192,11 +2191,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B84,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B84,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B84,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B84,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2211,11 +2210,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B85,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B85,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B85,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B85,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2230,11 +2229,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B86,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B86,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B86,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B86,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2249,11 +2248,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B87,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B87,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B87,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B87,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2268,11 +2267,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B88,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B88,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B88,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B88,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2287,11 +2286,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B89,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B89,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B89,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B89,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2306,11 +2305,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B90,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B90,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B90,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B90,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2325,11 +2324,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B91,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B91,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B91,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B91,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2344,11 +2343,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B92,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B92,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B92,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B92,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2363,11 +2362,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B93,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B93,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B93,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B93,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2382,11 +2381,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B94,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B94,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B94,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B94,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2401,11 +2400,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B95,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B95,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B95,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B95,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2420,11 +2419,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B96,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B96,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B96,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B96,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2439,11 +2438,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B97,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B97,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B97,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B97,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2458,11 +2457,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B98,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B98,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B98,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B98,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2477,11 +2476,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B99,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B99,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B99,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B99,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2496,11 +2495,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B100,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B100,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B100,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B100,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2515,11 +2514,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B101,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B101,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B101,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B101,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2534,11 +2533,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B102,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B102,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B102,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B102,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2553,11 +2552,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B103,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B103,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B103,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B103,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2572,11 +2571,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B104,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B104,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B104,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B104,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2591,11 +2590,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B105,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B105,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B105,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B105,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2610,11 +2609,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B106,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B106,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B106,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B106,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2629,11 +2628,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B107,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B107,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B107,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B107,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2648,11 +2647,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B108,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B108,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B108,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B108,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2667,11 +2666,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B109,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B109,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B109,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B109,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2686,11 +2685,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B110,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B110,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B110,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B110,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2705,11 +2704,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B111,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B111,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B111,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B111,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2724,11 +2723,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B112,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B112,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B112,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B112,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2743,11 +2742,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B113,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B113,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B113,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B113,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2762,11 +2761,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B114,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B114,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B114,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B114,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2781,11 +2780,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B115,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B115,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B115,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B115,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2800,11 +2799,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B116,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B116,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B116,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B116,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2819,11 +2818,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B117,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B117,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B117,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B117,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2838,11 +2837,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B118,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B118,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B118,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B118,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2857,11 +2856,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B119,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B119,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B119,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B119,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2876,11 +2875,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B120,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B120,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B120,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B120,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2895,11 +2894,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B121,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B121,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B121,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B121,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2914,11 +2913,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B122,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B122,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B122,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B122,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2933,11 +2932,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B123,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B123,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B123,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B123,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2952,11 +2951,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B124,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B124,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B124,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B124,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -2971,11 +2970,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B125,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B125,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B125,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B125,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -2990,11 +2989,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B126,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B126,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B126,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B126,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3009,11 +3008,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B127,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B127,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B127,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B127,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3028,11 +3027,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B128,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B128,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B128,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B128,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3047,11 +3046,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B129,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B129,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B129,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B129,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3066,11 +3065,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B130,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B130,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B130,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B130,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3085,11 +3084,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B131,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B131,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B131,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B131,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3104,11 +3103,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B132,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B132,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B132,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B132,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3123,11 +3122,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B133,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B133,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B133,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B133,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3142,11 +3141,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B134,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B134,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B134,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B134,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3161,11 +3160,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B135,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B135,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B135,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B135,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3180,11 +3179,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B136,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B136,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B136,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B136,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3199,11 +3198,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B137,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B137,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B137,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B137,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3218,11 +3217,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B138,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B138,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B138,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B138,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3237,11 +3236,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B139,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B139,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B139,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B139,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3256,11 +3255,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B140,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B140,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B140,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B140,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3275,11 +3274,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B141,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B141,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B141,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B141,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3294,11 +3293,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B142,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B142,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B142,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B142,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3313,11 +3312,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B143,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B143,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B143,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B143,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3332,11 +3331,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B144,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B144,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B144,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B144,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3351,11 +3350,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B145,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B145,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B145,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B145,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3370,11 +3369,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B146,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B146,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B146,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B146,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3389,11 +3388,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B147,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B147,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B147,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B147,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3408,11 +3407,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B148,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B148,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B148,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B148,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3427,11 +3426,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B149,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B149,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B149,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B149,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3446,11 +3445,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B150,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B150,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B150,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B150,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3465,11 +3464,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B151,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B151,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B151,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B151,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3484,11 +3483,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B152,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B152,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B152,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B152,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3503,11 +3502,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B153,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B153,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B153,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B153,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3522,11 +3521,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B154,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B154,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B154,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B154,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3541,11 +3540,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B155,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B155,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B155,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B155,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3560,11 +3559,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B156,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B156,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B156,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B156,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3579,11 +3578,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B157,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B157,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B157,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B157,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3598,11 +3597,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B158,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B158,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B158,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B158,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3617,11 +3616,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B159,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B159,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B159,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B159,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3636,11 +3635,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B160,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B160,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B160,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B160,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3655,11 +3654,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B161,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B161,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B161,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B161,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3674,11 +3673,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B162,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B162,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B162,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B162,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3693,11 +3692,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B163,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B163,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B163,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B163,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3712,11 +3711,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B164,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B164,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B164,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B164,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3731,11 +3730,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B165,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B165,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B165,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B165,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3750,11 +3749,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B166,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B166,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B166,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B166,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3769,11 +3768,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B167,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B167,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B167,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B167,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3788,11 +3787,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B168,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B168,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B168,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B168,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3807,11 +3806,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B169,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B169,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B169,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B169,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3826,11 +3825,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B170,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B170,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B170,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B170,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3845,11 +3844,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B171,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B171,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B171,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B171,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3864,11 +3863,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B172,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B172,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B172,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B172,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3883,11 +3882,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B173,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B173,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B173,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B173,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3902,11 +3901,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B174,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B174,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B174,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B174,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3921,11 +3920,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B175,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B175,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B175,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B175,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3940,11 +3939,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B176,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B176,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B176,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B176,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3959,11 +3958,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B177,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B177,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B177,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B177,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -3978,11 +3977,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B178,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B178,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B178,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B178,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -3997,11 +3996,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B179,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B179,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B179,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B179,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4016,11 +4015,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B180,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B180,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B180,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B180,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4035,11 +4034,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B181,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B181,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B181,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B181,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4054,11 +4053,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B182,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B182,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B182,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B182,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4073,11 +4072,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B183,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B183,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B183,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B183,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4092,11 +4091,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B184,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B184,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B184,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B184,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4111,11 +4110,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B185,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B185,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B185,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B185,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4130,11 +4129,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B186,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B186,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B186,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B186,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4149,11 +4148,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B187,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B187,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B187,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B187,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4168,11 +4167,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B188,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B188,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B188,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B188,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4187,11 +4186,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B189,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B189,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B189,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B189,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4206,11 +4205,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B190,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B190,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B190,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B190,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4225,11 +4224,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B191,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B191,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B191,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B191,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4244,11 +4243,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B192,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B192,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B192,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B192,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4263,11 +4262,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B193,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B193,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B193,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B193,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4282,11 +4281,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B194,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B194,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B194,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B194,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4301,11 +4300,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B195,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B195,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B195,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B195,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4320,11 +4319,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B196,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B196,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B196,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B196,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4339,11 +4338,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B197,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B197,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B197,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B197,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4358,11 +4357,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B198,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B198,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B198,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B198,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4377,11 +4376,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B199,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B199,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B199,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B199,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4396,11 +4395,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B200,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B200,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B200,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B200,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4415,11 +4414,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B201,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B201,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B201,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B201,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4434,11 +4433,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B202,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B202,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B202,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B202,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4453,11 +4452,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B203,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B203,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B203,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B203,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4472,11 +4471,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B204,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B204,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B204,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B204,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4491,11 +4490,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B205,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B205,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B205,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B205,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4510,11 +4509,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B206,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B206,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B206,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B206,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4529,11 +4528,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B207,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B207,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B207,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B207,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4548,11 +4547,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B208,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B208,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B208,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B208,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4567,11 +4566,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B209,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B209,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B209,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B209,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4586,11 +4585,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B210,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B210,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B210,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B210,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4605,11 +4604,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B211,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B211,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B211,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B211,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4624,11 +4623,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B212,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B212,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B212,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B212,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4643,11 +4642,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B213,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B213,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B213,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B213,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4662,11 +4661,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B214,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B214,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B214,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B214,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4681,11 +4680,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B215,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B215,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B215,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B215,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4700,11 +4699,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B216,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B216,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B216,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B216,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4719,11 +4718,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B217,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B217,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B217,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B217,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4738,11 +4737,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B218,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B218,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B218,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B218,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4757,11 +4756,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B219,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B219,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B219,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B219,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4776,11 +4775,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B220,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B220,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B220,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B220,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4795,11 +4794,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B221,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B221,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B221,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B221,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4814,11 +4813,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B222,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B222,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B222,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B222,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4833,11 +4832,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B223,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B223,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B223,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B223,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4852,11 +4851,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B224,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B224,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B224,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B224,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4871,11 +4870,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B225,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B225,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B225,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B225,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4890,11 +4889,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B226,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B226,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B226,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B226,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4909,11 +4908,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B227,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B227,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B227,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B227,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4928,11 +4927,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B228,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B228,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B228,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B228,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4947,11 +4946,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B229,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B229,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B229,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B229,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -4966,11 +4965,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B230,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B230,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B230,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B230,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -4985,11 +4984,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B231,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B231,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B231,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B231,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5004,11 +5003,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B232,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B232,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B232,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B232,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5023,11 +5022,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B233,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B233,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B233,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B233,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5042,11 +5041,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B234,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B234,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B234,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B234,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5061,11 +5060,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B235,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B235,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B235,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B235,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5080,11 +5079,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B236,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B236,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B236,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B236,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5099,11 +5098,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B237,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B237,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B237,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B237,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5118,11 +5117,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B238,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B238,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B238,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B238,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5137,11 +5136,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B239,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B239,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B239,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B239,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5156,11 +5155,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B240,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B240,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B240,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B240,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5175,11 +5174,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B241,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B241,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B241,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B241,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5194,11 +5193,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B242,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B242,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B242,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B242,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5213,11 +5212,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B243,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B243,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B243,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B243,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5232,11 +5231,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B244,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B244,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B244,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B244,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5251,11 +5250,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B245,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B245,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B245,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B245,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5270,11 +5269,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B246,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B246,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B246,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B246,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5289,11 +5288,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B247,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B247,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B247,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B247,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5308,11 +5307,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B248,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B248,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B248,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B248,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5327,11 +5326,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B249,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B249,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B249,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B249,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5346,11 +5345,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B250,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B250,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B250,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B250,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5365,11 +5364,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B251,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B251,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B251,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B251,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5384,11 +5383,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B252,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B252,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B252,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B252,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5403,11 +5402,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B253,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B253,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B253,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B253,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5422,11 +5421,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B254,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B254,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B254,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B254,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5441,11 +5440,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B255,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B255,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B255,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B255,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5460,11 +5459,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B256,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B256,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B256,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B256,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5479,11 +5478,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B257,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B257,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B257,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B257,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5498,11 +5497,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B258,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B258,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B258,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B258,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5517,11 +5516,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B259,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B259,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B259,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B259,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5536,11 +5535,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B260,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B260,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B260,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B260,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5555,11 +5554,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B261,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B261,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B261,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B261,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5574,11 +5573,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B262,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B262,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B262,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B262,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5593,11 +5592,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B263,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B263,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B263,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B263,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5612,11 +5611,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B264,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B264,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B264,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B264,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5631,11 +5630,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B265,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B265,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B265,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B265,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5650,11 +5649,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B266,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B266,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B266,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B266,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5669,11 +5668,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B267,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B267,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B267,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B267,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5688,11 +5687,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B268,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B268,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B268,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B268,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5707,11 +5706,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B269,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B269,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B269,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B269,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5726,11 +5725,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B270,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B270,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B270,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B270,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5745,11 +5744,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B271,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B271,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B271,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B271,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5764,11 +5763,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B272,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B272,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B272,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B272,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5783,11 +5782,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B273,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B273,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B273,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B273,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5802,11 +5801,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B274,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B274,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B274,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B274,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5821,11 +5820,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B275,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B275,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B275,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B275,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5840,11 +5839,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B276,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B276,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B276,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B276,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5859,11 +5858,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B277,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B277,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B277,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B277,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5878,11 +5877,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B278,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B278,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B278,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B278,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5897,11 +5896,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B279,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B279,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B279,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B279,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5916,11 +5915,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B280,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B280,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B280,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B280,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5935,11 +5934,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B281,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B281,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B281,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B281,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5954,11 +5953,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B282,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B282,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B282,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B282,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -5973,11 +5972,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B283,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B283,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B283,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B283,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -5992,11 +5991,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B284,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B284,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B284,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B284,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6011,11 +6010,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B285,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B285,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B285,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B285,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6030,11 +6029,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B286,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B286,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B286,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B286,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6049,11 +6048,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B287,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B287,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B287,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B287,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6068,11 +6067,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B288,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B288,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B288,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B288,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6087,11 +6086,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B289,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B289,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B289,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B289,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6106,11 +6105,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B290,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B290,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B290,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B290,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6125,11 +6124,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B291,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B291,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B291,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B291,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6144,11 +6143,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B292,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B292,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B292,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B292,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6163,11 +6162,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B293,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B293,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B293,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B293,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6182,11 +6181,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B294,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B294,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B294,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B294,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6201,11 +6200,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B295,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B295,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B295,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B295,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6220,11 +6219,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B296,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B296,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B296,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B296,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6239,11 +6238,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B297,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B297,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B297,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B297,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6258,11 +6257,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B298,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B298,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B298,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B298,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6277,11 +6276,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B299,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B299,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B299,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B299,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6296,11 +6295,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B300,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B300,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B300,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B300,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6315,11 +6314,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B301,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B301,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B301,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B301,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6334,11 +6333,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B302,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B302,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B302,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B302,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6353,11 +6352,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B303,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B303,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B303,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B303,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6372,11 +6371,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B304,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B304,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B304,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B304,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6391,11 +6390,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B305,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B305,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B305,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B305,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6410,11 +6409,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B306,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B306,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B306,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B306,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6429,11 +6428,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B307,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B307,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B307,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B307,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6448,11 +6447,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B308,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B308,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B308,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B308,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6467,11 +6466,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B309,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B309,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B309,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B309,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6486,11 +6485,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B310,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B310,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B310,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B310,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6505,11 +6504,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B311,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B311,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B311,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B311,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6524,11 +6523,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B312,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B312,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B312,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B312,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6543,11 +6542,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B313,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B313,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B313,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B313,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6562,11 +6561,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B314,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B314,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B314,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B314,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6581,11 +6580,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B315,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B315,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B315,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B315,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6600,11 +6599,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B316,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B316,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B316,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B316,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6619,11 +6618,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B317,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B317,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B317,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B317,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6638,11 +6637,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B318,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B318,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B318,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B318,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6657,11 +6656,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B319,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B319,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B319,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B319,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6676,11 +6675,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B320,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B320,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B320,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B320,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6695,11 +6694,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B321,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B321,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B321,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B321,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6714,11 +6713,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B322,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B322,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B322,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B322,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6733,11 +6732,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B323,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B323,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B323,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B323,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6752,11 +6751,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B324,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B324,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B324,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B324,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6771,11 +6770,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B325,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B325,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B325,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B325,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6790,11 +6789,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B326,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B326,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B326,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B326,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6809,11 +6808,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B327,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B327,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B327,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B327,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6828,11 +6827,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B328,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B328,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B328,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B328,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6847,11 +6846,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B329,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B329,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B329,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B329,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6866,11 +6865,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B330,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B330,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B330,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B330,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6885,11 +6884,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B331,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B331,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B331,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B331,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6904,11 +6903,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B332,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B332,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B332,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B332,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6923,11 +6922,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B333,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B333,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B333,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B333,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6942,11 +6941,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B334,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B334,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B334,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B334,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6961,11 +6960,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B335,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B335,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B335,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B335,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -6980,11 +6979,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B336,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B336,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B336,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B336,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -6999,11 +6998,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B337,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B337,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B337,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B337,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7018,11 +7017,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B338,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B338,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B338,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B338,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7037,11 +7036,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B339,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B339,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B339,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B339,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7056,11 +7055,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B340,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B340,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B340,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B340,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7075,11 +7074,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B341,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B341,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B341,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B341,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7094,11 +7093,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B342,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B342,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B342,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B342,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7113,11 +7112,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B343,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B343,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B343,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B343,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7132,11 +7131,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B344,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B344,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B344,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B344,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7151,11 +7150,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B345,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B345,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B345,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B345,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7170,11 +7169,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B346,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B346,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B346,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B346,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7189,11 +7188,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B347,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B347,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B347,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B347,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7208,11 +7207,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B348,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B348,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B348,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B348,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7227,11 +7226,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B349,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B349,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B349,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B349,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7246,11 +7245,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B350,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B350,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B350,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B350,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7265,11 +7264,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B351,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B351,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B351,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B351,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7284,11 +7283,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B352,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B352,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B352,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B352,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7303,11 +7302,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B353,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B353,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B353,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B353,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7322,11 +7321,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B354,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B354,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B354,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B354,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7341,11 +7340,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B355,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B355,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B355,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B355,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7360,11 +7359,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B356,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B356,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B356,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B356,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7379,11 +7378,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B357,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B357,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B357,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B357,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7398,11 +7397,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B358,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B358,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B358,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B358,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7417,11 +7416,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B359,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B359,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B359,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B359,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7436,11 +7435,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B360,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B360,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B360,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B360,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7455,11 +7454,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B361,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B361,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B361,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B361,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7474,11 +7473,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B362,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B362,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B362,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B362,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7493,11 +7492,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B363,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B363,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B363,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B363,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7512,11 +7511,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B364,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B364,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B364,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B364,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7531,11 +7530,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B365,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B365,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B365,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B365,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7550,11 +7549,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B366,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B366,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B366,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B366,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7569,11 +7568,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B367,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B367,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B367,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B367,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7588,11 +7587,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B368,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B368,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B368,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B368,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7607,11 +7606,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B369,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B369,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B369,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B369,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7626,11 +7625,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B370,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B370,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B370,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B370,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7645,11 +7644,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B371,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B371,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B371,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B371,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7664,11 +7663,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B372,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B372,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B372,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B372,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7683,11 +7682,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B373,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B373,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B373,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B373,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7702,11 +7701,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B374,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B374,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B374,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B374,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7721,11 +7720,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B375,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B375,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B375,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B375,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7740,11 +7739,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B376,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B376,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B376,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B376,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7759,11 +7758,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B377,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B377,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B377,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B377,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7778,11 +7777,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B378,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B378,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B378,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B378,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7797,11 +7796,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B379,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B379,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B379,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B379,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7816,11 +7815,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B380,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B380,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B380,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B380,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7835,11 +7834,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B381,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B381,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B381,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B381,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7854,11 +7853,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B382,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B382,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B382,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B382,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7873,11 +7872,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B383,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B383,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B383,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B383,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7892,11 +7891,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B384,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B384,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B384,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B384,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7911,11 +7910,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B385,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B385,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B385,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B385,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7930,11 +7929,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B386,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B386,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B386,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B386,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7949,11 +7948,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B387,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B387,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B387,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B387,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -7968,11 +7967,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B388,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B388,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B388,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B388,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -7987,11 +7986,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B389,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B389,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B389,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B389,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8006,11 +8005,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B390,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B390,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B390,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B390,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8025,11 +8024,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B391,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B391,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B391,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B391,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8044,11 +8043,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B392,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B392,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B392,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B392,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8063,11 +8062,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B393,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B393,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B393,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B393,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8082,11 +8081,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B394,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B394,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B394,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B394,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8101,11 +8100,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B395,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B395,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B395,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B395,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8120,11 +8119,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B396,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B396,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B396,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B396,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8139,11 +8138,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B397,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B397,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B397,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B397,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8158,11 +8157,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B398,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B398,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B398,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B398,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8177,11 +8176,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B399,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B399,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B399,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B399,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8196,11 +8195,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B400,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B400,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B400,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B400,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8215,11 +8214,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B401,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B401,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B401,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B401,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8234,11 +8233,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$90,MATCH(B402,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$88,MATCH(B402,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$90,MATCH(B402,Productos!$A$2:$A$90,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$88,MATCH(B402,Productos!$A$2:$A$88,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -8279,7 +8278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8345,55 +8344,50 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>OLA</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PERKY PET</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>RED BARN</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SYNERGY</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>SYNERGY</t>
+          <t>TETRA</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
-        <is>
-          <t>TETRA</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
         <is>
           <t>WHISKAS</t>
         </is>
@@ -8461,55 +8455,50 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
+          <t>OLA LOROS GUACAMAYA/PARROTS 800GRS · 90405590000</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>OLA LOROS GUACAMAYA/PARROTS 800GRS · 90405590000</t>
+          <t>NECTAR INSTANTANEO DE COLIBRI 2LB · 90710077000</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>NECTAR INSTANTANEO DE COLIBRI 2LB · 90710077000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
+          <t>D SUPRA ADULTO 10KG · 93508880000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>D SUPRA ADULTO 10KG · 93508880000</t>
+          <t>SHED-X SUPLEMENTO PERROS GRANDES · 90334000000</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>SHED-X SUPLEMENTO PERROS GRANDES · 90334000000</t>
+          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
-        <is>
-          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
         <is>
           <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
         </is>
@@ -8565,37 +8554,37 @@
           <t>MIMADOS ADULTO 2KG · 90400360000</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
           <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
         </is>
       </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>D SK ALIM LATA RES/HIGADO POLLO 400GR · 93511640000</t>
+        </is>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES/HIGADO POLLO 400GR · 93511640000</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
           <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
+        </is>
+      </c>
       <c r="V3" t="inlineStr">
-        <is>
-          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
         <is>
           <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
         </is>
@@ -8646,32 +8635,32 @@
           <t>MIMADOS ADULTOS 4KG · 93513340000</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
           <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+        </is>
+      </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
           <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
-        <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
         <is>
           <t>WHISKAS POUCH RES  85GR · 90409070000</t>
         </is>
@@ -8704,7 +8693,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>PA LECHE DE CABRA EN POLVO 150GM · 93519340000</t>
+          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -8717,27 +8706,27 @@
           <t>MIMADOS CACHORRO  2KG · 90400340000</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
           <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
         </is>
       </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
+        </is>
+      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
           <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>TETRAFIN PELLET FLOTANTE 1.87OZ · 90410020000</t>
         </is>
@@ -8756,7 +8745,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
+          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -8769,27 +8758,27 @@
           <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
           <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
         </is>
       </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ROCKY ALIM P/CACHORROS 1.5KG · 93512600000</t>
+        </is>
+      </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>ROCKY ALIM P/CACHORROS 1.5KG · 93512600000</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
           <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>TETRAMIN HOJUELAS 3.53 OZ. · 90720600000</t>
         </is>
@@ -8806,27 +8795,22 @@
           <t>MARCA_6</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
           <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
         </is>
       </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+        </is>
+      </c>
       <c r="S7" t="inlineStr">
-        <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
         <is>
           <t>SUPRA ADULTO 4KG · 93508870000</t>
         </is>
@@ -8843,17 +8827,17 @@
           <t>MARCA_7</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
           <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
         </is>
@@ -8870,17 +8854,17 @@
           <t>MARCA_8</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
           <t>NS CHOICE PESCADO Y ARROZ 40LB · 90034150000</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
@@ -8897,12 +8881,12 @@
           <t>MARCA_9</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
         <is>
           <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
         </is>
@@ -8911,7 +8895,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8919,12 +8903,12 @@
           <t>MARCA_10</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
         <is>
           <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
         </is>
@@ -8933,7 +8917,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -8941,12 +8925,12 @@
           <t>MARCA_11</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
         <is>
           <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
         </is>
@@ -8955,7 +8939,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>OLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8963,12 +8947,12 @@
           <t>MARCA_12</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
         <is>
           <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
         </is>
@@ -8977,7 +8961,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PERKY PET</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8985,12 +8969,12 @@
           <t>MARCA_13</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
-        <is>
-          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
         <is>
           <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
         </is>
@@ -8999,7 +8983,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>RED BARN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -9007,7 +8991,7 @@
           <t>MARCA_14</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
@@ -9016,7 +9000,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -9024,7 +9008,7 @@
           <t>MARCA_15</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
         </is>
@@ -9033,7 +9017,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -9041,7 +9025,7 @@
           <t>MARCA_16</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
         </is>
@@ -9050,7 +9034,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SYNERGY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -9058,7 +9042,7 @@
           <t>MARCA_17</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
@@ -9067,7 +9051,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SYNERGY</t>
+          <t>TETRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9079,24 +9063,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>WHISKAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>MARCA_19</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>WHISKAS</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>MARCA_20</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9399,12 +9371,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PA LECHE DE CABRA EN POLVO 150GM · 93519340000</t>
+          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>93519340000</t>
+          <t>93519360000</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -9419,16 +9391,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PETLAC LECHE EN POLVO P/PERROS 10.5 · 93519360000</t>
+          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>93519360000</t>
+          <t>90308700000</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -9439,56 +9411,56 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SUPL EN POLVO LECHE DE CABRA 12OZ · 90308700000</t>
+          <t>EUK DOG SMALL ADULT 1 Kg (2.20 lbs) · 90018540000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>90308700000</t>
+          <t>90018540000</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ESBILAC</t>
+          <t>EUKANUBA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EUK DOG SMALL ADULT 1 Kg (2.20 lbs) · 90018540000</t>
+          <t>SEM ALPISTE  1 LB · 90426180000</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>90018540000</t>
+          <t>90426180000</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EUKANUBA</t>
+          <t>GENÉRICO (reempaque)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEM ALPISTE  1 LB · 90426180000</t>
+          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>90426180000</t>
+          <t>90402150000</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -9499,16 +9471,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEMILLA DE GIRASOL 2 LB · 90402150000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>90402150000</t>
+          <t>90426190000</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -9519,16 +9491,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 454GR · 90426190000</t>
+          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>90426190000</t>
+          <t>90426200000</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -9539,12 +9511,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEMILLAS DE GIRASOL JUMBO 5 LB · 90426200000</t>
+          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90426200000</t>
+          <t>93500750000</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -9559,56 +9531,56 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEMILLAS DE MIJO VARIADAS 1LB · 93500750000</t>
+          <t>D GL SUPLEMENTO PIEL Y PELAJE 6OZ · 93500000215</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>93500750000</t>
+          <t>93500000215</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GENÉRICO (reempaque)</t>
+          <t>GRANDMA LUCY'S</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D GL SUPLEMENTO PIEL Y PELAJE 6OZ · 93500000215</t>
+          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>93500000215</t>
+          <t>90404930000</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GRANDMA LUCY'S</t>
+          <t>KAYTEE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KT ALIM. EXACT P PICHONES 18OZ. · 90404930000</t>
+          <t>KT EXACT PARA PICHONES 7.5 OZ · 90404920000</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90404930000</t>
+          <t>90404920000</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -9619,16 +9591,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KT EXACT PARA PICHONES 7.5 OZ · 90404920000</t>
+          <t>KT SUPREME PALOMA 6/5LB · 93500800000</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90404920000</t>
+          <t>93500800000</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -9639,36 +9611,36 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KT SUPREME PALOMA 6/5LB · 93500800000</t>
+          <t>MIMADOS ADULTO 18KG · 90409680000</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>93500800000</t>
+          <t>90409680000</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KAYTEE</t>
+          <t>MIMADOS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 18KG · 90409680000</t>
+          <t>MIMADOS ADULTO 2KG · 90400360000</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90409680000</t>
+          <t>90400360000</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -9679,16 +9651,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTO 2KG · 90400360000</t>
+          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90400360000</t>
+          <t>93513340000</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -9699,16 +9671,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MIMADOS ADULTOS 4KG · 93513340000</t>
+          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>93513340000</t>
+          <t>90400340000</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -9719,16 +9691,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORRO  2KG · 90400340000</t>
+          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>90400340000</t>
+          <t>93513280000</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -9739,56 +9711,56 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MIMADOS CACHORROS 4KG · 93513280000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>93513280000</t>
+          <t>93510820000</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MIMADOS</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MIRRAPEL PET POLVO 300 g · 90301720000</t>
+          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90301720000</t>
+          <t>93510810000</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MIRRAPEL</t>
+          <t>NUTRECAN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 2KG · 93510820000</t>
+          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>93510820000</t>
+          <t>93505910000</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -9799,16 +9771,16 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULT RZ PEQUENA 800 · 93510810000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>93510810000</t>
+          <t>93505950000</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -9819,16 +9791,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTO RM Y RG 800GR · 93505910000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>93505910000</t>
+          <t>93505960000</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>132</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -9839,16 +9811,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 16KG · 93505950000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>93505950000</t>
+          <t>93505920000</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -9859,16 +9831,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 25KG · 93505960000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>93505960000</t>
+          <t>93505930000</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -9879,16 +9851,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 2KG · 93505920000</t>
+          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>93505920000</t>
+          <t>93505940000</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -9899,16 +9871,16 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 4KG · 93505930000</t>
+          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>93505930000</t>
+          <t>90410720000</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -9919,16 +9891,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN ADULTOS RM Y RG 8KG · 93505940000</t>
+          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>93505940000</t>
+          <t>90410730000</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9939,16 +9911,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 0.8 KG · 90410720000</t>
+          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90410720000</t>
+          <t>90410970000</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -9959,16 +9931,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 2 KG · 90410730000</t>
+          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90410730000</t>
+          <t>90410800000</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -9979,12 +9951,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN BABIES 8 KG · 90410970000</t>
+          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>90410970000</t>
+          <t>90410820000</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -9999,16 +9971,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 0.8KG · 90410800000</t>
+          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>90410800000</t>
+          <t>90410830000</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -10019,16 +9991,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 16KG · 90410820000</t>
+          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>90410820000</t>
+          <t>90410810000</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -10039,16 +10011,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 25KG · 90410830000</t>
+          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>90410830000</t>
+          <t>93510840000</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10059,16 +10031,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN CAMPO 8KG · 90410810000</t>
+          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>90410810000</t>
+          <t>93510830000</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -10079,56 +10051,56 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 2KG · 93510840000</t>
+          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>93510840000</t>
+          <t>90034090000</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SOLLA NUTRECAN LIGHT 800GR · 93510830000</t>
+          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>93510830000</t>
+          <t>90033960000</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NUTRECAN</t>
+          <t>NUTRISOURCE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NS CHOICE CACHORR POLLO CEBADA 5LB · 90034090000</t>
+          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>90034090000</t>
+          <t>90034200000</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -10139,16 +10111,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NS CHOICE CARNE Y CEBADA 5LB · 90033960000</t>
+          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>90033960000</t>
+          <t>90034180000</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -10159,16 +10131,16 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CACHOR POLLO ARROZ 12.3OZ · 90034200000</t>
+          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>90034200000</t>
+          <t>90034290000</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -10179,12 +10151,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA CARNE Y CEBADA 12.3OZ · 90034180000</t>
+          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>90034180000</t>
+          <t>90034190000</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -10199,16 +10171,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA PAVO Y CEBADA 12.3OZ · 90034290000</t>
+          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>90034290000</t>
+          <t>90034130000</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -10219,16 +10191,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NS CHOICE LATA POLLO Y CEBADA 12.3OZ · 90034190000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 40LB · 90034150000</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>90034190000</t>
+          <t>90034150000</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -10239,12 +10211,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NS CHOICE PAVO Y CEBADA 5LB · 90034130000</t>
+          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>90034130000</t>
+          <t>90034160000</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -10259,16 +10231,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 40LB · 90034150000</t>
+          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>90034150000</t>
+          <t>90033990000</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -10279,16 +10251,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NS CHOICE PESCADO Y ARROZ 5LB · 90034160000</t>
+          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>90034160000</t>
+          <t>90034210000</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -10299,16 +10271,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NS CHOICE POLLO Y CEBADA 5LB · 90033990000</t>
+          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>90033990000</t>
+          <t>90034250000</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10319,16 +10291,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS CARNE 12OZ · 90034210000</t>
+          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>90034210000</t>
+          <t>90034230000</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -10339,136 +10311,136 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS PAVO 12OZ · 90034250000</t>
+          <t>OLA LOROS GUACAMAYA/PARROTS 800GRS · 90405590000</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>90034250000</t>
+          <t>90405590000</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>OLA</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NS CHOICE SNACK GRILLERS POLLO 12OZ · 90034230000</t>
+          <t>NECTAR INSTANTANEO DE COLIBRI 2LB · 90710077000</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>90034230000</t>
+          <t>90710077000</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NUTRISOURCE</t>
+          <t>PERKY PET</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OLA LOROS GUACAMAYA/PARROTS 800GRS · 90405590000</t>
+          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>90405590000</t>
+          <t>93502370000</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>OLA</t>
+          <t>PERKY PET</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>NECTAR INSTANTANEO DE COLIBRI 2LB · 90710077000</t>
+          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>90710077000</t>
+          <t>93512180000</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>RED BARN</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NECTAR PARA COLIBRI 240 · 93502370000</t>
+          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>93502370000</t>
+          <t>93511630000</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PERKY PET</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>D RB HUESO PQNO RELLENO DE POLLO · 93512180000</t>
+          <t>D SK ALIM LATA RES/HIGADO POLLO 400GR · 93511640000</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>93512180000</t>
+          <t>93511640000</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>RED BARN</t>
+          <t>SUPERKAN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES Y TOCINO 400GR · 93511630000</t>
+          <t>ROCKY ADULTOS 1KG · 93500000342</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>93511630000</t>
+          <t>93500000342</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -10479,16 +10451,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>D SK ALIM LATA RES/HIGADO POLLO 400GR · 93511640000</t>
+          <t>ROCKY ADULTOS 500G · 93500000341</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>93511640000</t>
+          <t>93500000341</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -10499,16 +10471,16 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 1KG · 93500000342</t>
+          <t>ROCKY ALIM P/CACHORROS 1.5KG · 93512600000</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>93500000342</t>
+          <t>93512600000</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10519,16 +10491,16 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ROCKY ADULTOS 500G · 93500000341</t>
+          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>93500000341</t>
+          <t>93511670000</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10539,56 +10511,56 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ROCKY ALIM P/CACHORROS 1.5KG · 93512600000</t>
+          <t>D SUPRA ADULTO 10KG · 93508880000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>93512600000</t>
+          <t>93508880000</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SK ALIM LATA POLLO/VEGETALES 400GR · 93511670000</t>
+          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>93511670000</t>
+          <t>93509320000</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SUPERKAN</t>
+          <t>SUPRA</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>D SUPRA ADULTO 10KG · 93508880000</t>
+          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>93508880000</t>
+          <t>93508860000</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10599,16 +10571,16 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>D SUPRA SNACK TOCINETAS P/PERRO · 93509320000</t>
+          <t>SUPRA ADULTO 18KG · 93508890000</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>93509320000</t>
+          <t>93508890000</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10619,16 +10591,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 1.5KG · 93508860000</t>
+          <t>SUPRA ADULTO 30KG · 93508900000</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>93508860000</t>
+          <t>93508900000</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10639,16 +10611,16 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 18KG · 93508890000</t>
+          <t>SUPRA ADULTO 4KG · 93508870000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>93508890000</t>
+          <t>93508870000</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10659,16 +10631,16 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 30KG · 93508900000</t>
+          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>93508900000</t>
+          <t>93508910000</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10679,12 +10651,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SUPRA ADULTO 4KG · 93508870000</t>
+          <t>SUPRA CACHORRO 4KG · 93508920000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>93508870000</t>
+          <t>93508920000</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -10699,76 +10671,76 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 1.5KG · 93508910000</t>
+          <t>SHED-X SUPLEMENTO PERROS GRANDES · 90334000000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>93508910000</t>
+          <t>90334000000</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SYNERGY</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
+          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>93508920000</t>
+          <t>90409640000</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SHED-X SUPLEMENTO PERROS GRANDES · 90334000000</t>
+          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>90334000000</t>
+          <t>90409900000</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SYNERGY</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>90409640000</t>
+          <t>90410990000</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10779,16 +10751,16 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
+          <t>TETRAFIN PELLET FLOTANTE 1.87OZ · 90410020000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>90409900000</t>
+          <t>90410020000</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10799,16 +10771,16 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
+          <t>TETRAMIN HOJUELAS 3.53 OZ. · 90720600000</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>90410990000</t>
+          <t>90720600000</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10819,78 +10791,58 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TETRAFIN PELLET FLOTANTE 1.87OZ · 90410020000</t>
+          <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>90410020000</t>
+          <t>90409060000</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>WHISKAS</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TETRAMIN HOJUELAS 3.53 OZ. · 90720600000</t>
+          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>90720600000</t>
+          <t>90409050000</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>WHISKAS</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH ATUN  85GR · 90409060000</t>
+          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>90409060000</t>
+          <t>90409070000</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D88" t="inlineStr">
-        <is>
-          <t>WHISKAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>90409050000</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>21</v>
-      </c>
-      <c r="D89" t="inlineStr">
         <is>
           <t>WHISKAS</t>
         </is>
@@ -10899,54 +10851,34 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
+          <t>Sucursal</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>90409070000</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>22</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>WHISKAS</t>
-        </is>
+          <t>MELO &amp; CIA. | PASO CANOAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sucursal</t>
+          <t>Inventario al</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MELO &amp; CIA. | PASO CANOAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Inventario al</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>29.10.2026</t>
+          <t>30.10.2026</t>
         </is>
       </c>
     </row>
